--- a/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Collegetown_2025-10-24.xlsx
+++ b/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Collegetown_2025-10-24.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>26.00</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>18.50</t>
         </is>
       </c>
     </row>
